--- a/shared/words/E2_单词汇总.xlsx
+++ b/shared/words/E2_单词汇总.xlsx
@@ -1859,6 +1859,11 @@
       <c r="F10" t="s">
         <v>42</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er antwortet schnell.</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -1873,6 +1878,11 @@
       <c r="F11" t="s">
         <v>45</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schließen Sie bitte die Bücher!</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
@@ -1904,6 +1914,11 @@
       <c r="F13" t="s">
         <v>52</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich studiere Physik.</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
@@ -1918,6 +1933,11 @@
       <c r="F14" t="s">
         <v>55</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wohnst du auch im Studentenwohnheim?</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
@@ -1932,6 +1952,11 @@
       <c r="F15" t="s">
         <v>58</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich schreibe einen Brief.</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
@@ -2032,6 +2057,11 @@
       <c r="F20" t="s">
         <v>83</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist mein Vorname.</t>
+        </is>
+      </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
@@ -2052,6 +2082,11 @@
       <c r="F21" t="s">
         <v>86</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie ist Ihr Familienname?</t>
+        </is>
+      </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
@@ -2164,6 +2199,11 @@
       <c r="F26" t="s">
         <v>106</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich studiere hier Chemie.</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
@@ -2184,6 +2224,11 @@
       <c r="F27" t="s">
         <v>109</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich studiere Informatik.</t>
+        </is>
+      </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
@@ -2204,6 +2249,11 @@
       <c r="F28" t="s">
         <v>112</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich studiere Elektrotechnik.</t>
+        </is>
+      </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
@@ -2224,6 +2274,11 @@
       <c r="F29" t="s">
         <v>116</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wohnst du auch im Studentenwohnheim?</t>
+        </is>
+      </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
@@ -2376,6 +2431,11 @@
       <c r="F36" t="s">
         <v>145</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hier sind zwei Pässe.</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
@@ -2390,6 +2450,11 @@
       <c r="F37" t="s">
         <v>148</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bitte sprechen Sie langsam.</t>
+        </is>
+      </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
@@ -2404,6 +2469,11 @@
       <c r="F38" t="s">
         <v>151</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist zu teuer.</t>
+        </is>
+      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
@@ -2554,6 +2624,11 @@
       <c r="F47" t="s">
         <v>185</v>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ist der Platz hier frei?</t>
+        </is>
+      </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
@@ -2568,6 +2643,11 @@
       <c r="F48" t="s">
         <v>188</v>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie heißt das noch mal auf Deutsch?</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
@@ -2582,6 +2662,11 @@
       <c r="F49" t="s">
         <v>191</v>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wo ist die Mensa?</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
@@ -2595,6 +2680,11 @@
       </c>
       <c r="F50" t="s">
         <v>194</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Übrigens, mein Name ist Wang.</t>
+        </is>
       </c>
     </row>
     <row r="51" spans="1:7">
